--- a/Lista para Armador pc.xlsx
+++ b/Lista para Armador pc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\user usuario\LandingPage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{680B05B0-A741-4BBB-8E85-89030BAA8ED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C3D52D1-385B-4970-9962-9452464BEB3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20280" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="91">
   <si>
     <t>Componente</t>
   </si>
@@ -505,6 +505,12 @@
   </si>
   <si>
     <t>Coler CPU</t>
+  </si>
+  <si>
+    <t>MOTHER MSI (AM4) A520M-A PRO</t>
+  </si>
+  <si>
+    <t>MOTHER GIGABYTE (AM4) A520M K V2</t>
   </si>
 </sst>
 </file>
@@ -885,7 +891,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E88"/>
+  <dimension ref="A1:E90"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="82.28515625" bestFit="1" customWidth="1"/>
@@ -1326,232 +1332,248 @@
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>47</v>
+        <v>90</v>
       </c>
       <c r="B59" s="2">
-        <v>91200</v>
+        <v>84500</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="B60" s="2">
-        <v>92200</v>
+        <v>84000</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B61" s="2">
-        <v>147300</v>
+        <v>91200</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B62" s="2">
-        <v>148700</v>
+        <v>92200</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B63" s="2">
-        <v>252600</v>
+        <v>147300</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B64" s="2">
-        <v>311000</v>
+        <v>148700</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B65" s="2">
+        <v>252600</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B66" s="2">
+        <v>311000</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="7" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B66" s="2">
+      <c r="B68" s="2">
         <v>37000</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B67" s="2">
+      <c r="B69" s="2">
         <v>68200</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" s="7" t="s">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="B68" s="2">
+      <c r="B70" s="2">
         <v>77900</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="B69" s="2">
-        <v>86000</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B70" s="2">
-        <v>123600</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B71" s="2">
+        <v>86000</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B72" s="2">
+        <v>123600</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B71" s="2">
+      <c r="B73" s="2">
         <v>135900</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72" s="7" t="s">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B72" s="2">
+      <c r="B74" s="2">
         <v>138200</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" s="1" t="s">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B73" s="2">
+      <c r="B75" s="2">
         <v>219900</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B74" s="2">
+      <c r="B76" s="2">
         <v>222300</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="B75" s="2">
-        <v>222637</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A76" s="7" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B77" s="2">
-        <v>90400</v>
+        <v>222637</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="B78" s="2">
-        <v>92800</v>
+        <v>75</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B79" s="2">
-        <v>143000</v>
+        <v>90400</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B80" s="2">
-        <v>144500</v>
+        <v>92800</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B81" s="2">
-        <v>210900</v>
+        <v>143000</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" s="7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B82" s="2">
-        <v>288400</v>
+        <v>144500</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B83" s="2">
-        <v>295000</v>
+        <v>210900</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" s="7" t="s">
-        <v>74</v>
+        <v>68</v>
+      </c>
+      <c r="B84" s="2">
+        <v>288400</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B85" s="2">
-        <v>44700</v>
+        <v>295000</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="B86" s="2">
-        <v>36686</v>
+        <v>74</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B87" s="2">
-        <v>35900</v>
+        <v>44700</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B88" s="2">
+        <v>36686</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="B89" s="2">
+        <v>35900</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="B88" s="2">
+      <c r="B90" s="2">
         <v>37300</v>
       </c>
     </row>
